--- a/xlsx/packagedata template-alt3.xlsx
+++ b/xlsx/packagedata template-alt3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9E0696-9C38-4801-99B7-FF696D5B7F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5C9442-01A0-4CAB-8F80-30AED8B1CFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,11 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
-  <si>
-    <t>单向可叉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>双向可叉</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -496,51 +492,51 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
       <c r="N1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>154143</v>
+        <v>154142</v>
       </c>
       <c r="B2">
         <v>110</v>
@@ -552,34 +548,34 @@
         <v>70</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>114.3</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -596,34 +592,34 @@
         <v>70</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>427.3</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L3">
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -640,34 +636,34 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>787.6</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
